--- a/ch_02/ch_02_solution.xlsx
+++ b/ch_02/ch_02_solution.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30515"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_02_pandas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611EEF9E-71F0-45CB-86D0-DAF510D771B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BAB798-30DC-45AB-BE45-757F4853DD5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="14586" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="nyc" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 <file path=xl/python.xml><?xml version="1.0" encoding="utf-8"?>
 <python xmlns="http://schemas.microsoft.com/office/spreadsheetml/2023/python">
   <environmentDefinition id="{882DD1B0-6546-4DFA-8A08-902A380B44EA}">
-    <initialization userModified="1">
+    <initialization>
       <code xml:space="preserve">import numpy as np
 import pandas as pd
 import matplotlib.pyplot as plt
@@ -111,7 +111,7 @@
     </pythonScript>
     <pythonScript>
       <code xml:space="preserve"># Find %% of missing values in each column
-sales_df.isna().mean() / 100 </code>
+sales_df.isna().mean() * 100 </code>
     </pythonScript>
     <pythonScript>
       <code>sales_df.isna().mean().sort_values(ascending=False) * 100</code>
@@ -1214,7 +1214,7 @@
     </spb>
     <spb s="2">
       <v>https://www.anaconda.com/excel</v>
-      <v>https://res.cdn.office.net/officepysvc/prod-service/anacondalogo.png</v>
+      <v>https://res.cdn.office.net/officepysvc/prod-preview/anacondalogo.png</v>
       <v>Python provided by Anaconda</v>
     </spb>
   </spbData>
@@ -1555,18 +1555,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="14" style="4" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="5" max="5" width="10.87890625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.64453125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="11.05859375" style="5" customWidth="1"/>
-    <col min="8" max="8" width="8.9375" style="5"/>
+    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.6640625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.06640625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="8.9296875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1590,7 +1590,7 @@
         <v>density</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1598,7 +1598,7 @@
         <v>2736074</v>
       </c>
       <c r="C2">
-        <v>69.37</v>
+        <v>69.5</v>
       </c>
       <c r="E2" t="str">
         <v>Brooklyn</v>
@@ -1607,13 +1607,13 @@
         <v>2736074</v>
       </c>
       <c r="G2" s="5">
-        <v>69.37</v>
+        <v>69.5</v>
       </c>
       <c r="H2" s="5">
-        <v>39441.747152947959</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.5">
+        <v>39367.971223021581</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1621,7 +1621,7 @@
         <v>2405464</v>
       </c>
       <c r="C3">
-        <v>108.53</v>
+        <v>108.7</v>
       </c>
       <c r="E3" t="str">
         <v>Queens</v>
@@ -1630,13 +1630,13 @@
         <v>2405464</v>
       </c>
       <c r="G3" s="5">
-        <v>108.53</v>
+        <v>108.7</v>
       </c>
       <c r="H3" s="5">
-        <v>22164.046807334376</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.5">
+        <v>22129.383624655013</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>74211.607533946561</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>237</v>
       </c>
@@ -1682,7 +1682,7 @@
         <v>34979.904988123511</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1705,33 +1705,33 @@
         <v>8493.1814288161731</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="E8" t="str" cm="1">
         <f t="array" ref="E8:E13">_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(E1), 2)</f>
         <v>population</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="E9">
         <v>2736074</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="E10">
         <v>2405464</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="E11">
         <v>1694251</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="E12">
         <v>1472654</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="E13">
         <v>495747</v>
       </c>
@@ -1747,7 +1747,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G201"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -1758,7 +1758,7 @@
     <col min="7" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -1781,7 +1781,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -1850,7 +1850,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -1896,7 +1896,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -1919,7 +1919,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -2080,7 +2080,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -2103,7 +2103,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -2126,7 +2126,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -2149,7 +2149,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -2172,7 +2172,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -2264,7 +2264,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>52</v>
       </c>
@@ -2287,7 +2287,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -2333,7 +2333,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>57</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>59</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -2402,7 +2402,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>61</v>
       </c>
@@ -2425,7 +2425,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>62</v>
       </c>
@@ -2448,7 +2448,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -2471,7 +2471,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>65</v>
       </c>
@@ -2494,7 +2494,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>66</v>
       </c>
@@ -2517,7 +2517,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>67</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>68</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>69</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>70</v>
       </c>
@@ -2609,7 +2609,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>72</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>73</v>
       </c>
@@ -2655,7 +2655,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>74</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>76</v>
       </c>
@@ -2701,7 +2701,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>77</v>
       </c>
@@ -2724,7 +2724,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>78</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>79</v>
       </c>
@@ -2770,7 +2770,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>80</v>
       </c>
@@ -2793,7 +2793,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>81</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>82</v>
       </c>
@@ -2839,7 +2839,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>83</v>
       </c>
@@ -2862,7 +2862,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>84</v>
       </c>
@@ -2885,7 +2885,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>85</v>
       </c>
@@ -2908,7 +2908,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>86</v>
       </c>
@@ -2931,7 +2931,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>87</v>
       </c>
@@ -2954,7 +2954,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>88</v>
       </c>
@@ -2977,7 +2977,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>89</v>
       </c>
@@ -3000,7 +3000,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>90</v>
       </c>
@@ -3023,7 +3023,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>91</v>
       </c>
@@ -3046,7 +3046,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>92</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>93</v>
       </c>
@@ -3092,7 +3092,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>94</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -3138,7 +3138,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>96</v>
       </c>
@@ -3161,7 +3161,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>97</v>
       </c>
@@ -3184,7 +3184,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>98</v>
       </c>
@@ -3207,7 +3207,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>99</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>100</v>
       </c>
@@ -3253,7 +3253,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>101</v>
       </c>
@@ -3273,7 +3273,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>102</v>
       </c>
@@ -3296,7 +3296,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>103</v>
       </c>
@@ -3319,7 +3319,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>104</v>
       </c>
@@ -3342,7 +3342,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>105</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>106</v>
       </c>
@@ -3388,7 +3388,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>107</v>
       </c>
@@ -3411,7 +3411,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>108</v>
       </c>
@@ -3434,7 +3434,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>109</v>
       </c>
@@ -3457,7 +3457,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>110</v>
       </c>
@@ -3480,7 +3480,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>111</v>
       </c>
@@ -3503,7 +3503,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>112</v>
       </c>
@@ -3526,7 +3526,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>113</v>
       </c>
@@ -3549,7 +3549,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>114</v>
       </c>
@@ -3572,7 +3572,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>115</v>
       </c>
@@ -3595,7 +3595,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>116</v>
       </c>
@@ -3618,7 +3618,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>117</v>
       </c>
@@ -3641,7 +3641,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>118</v>
       </c>
@@ -3664,7 +3664,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>119</v>
       </c>
@@ -3687,7 +3687,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>120</v>
       </c>
@@ -3710,7 +3710,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>121</v>
       </c>
@@ -3733,7 +3733,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>122</v>
       </c>
@@ -3756,7 +3756,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>123</v>
       </c>
@@ -3779,7 +3779,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>124</v>
       </c>
@@ -3802,7 +3802,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>125</v>
       </c>
@@ -3825,7 +3825,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>126</v>
       </c>
@@ -3848,7 +3848,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>127</v>
       </c>
@@ -3871,7 +3871,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>128</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>129</v>
       </c>
@@ -3917,7 +3917,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>130</v>
       </c>
@@ -3940,7 +3940,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>131</v>
       </c>
@@ -3963,7 +3963,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>132</v>
       </c>
@@ -3986,7 +3986,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>133</v>
       </c>
@@ -4009,7 +4009,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>134</v>
       </c>
@@ -4032,7 +4032,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>135</v>
       </c>
@@ -4055,7 +4055,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>136</v>
       </c>
@@ -4078,7 +4078,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>137</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>138</v>
       </c>
@@ -4124,7 +4124,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>139</v>
       </c>
@@ -4147,7 +4147,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>140</v>
       </c>
@@ -4170,7 +4170,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>141</v>
       </c>
@@ -4193,7 +4193,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>142</v>
       </c>
@@ -4216,7 +4216,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>143</v>
       </c>
@@ -4239,7 +4239,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>144</v>
       </c>
@@ -4262,7 +4262,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>145</v>
       </c>
@@ -4285,7 +4285,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>146</v>
       </c>
@@ -4308,7 +4308,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>147</v>
       </c>
@@ -4331,7 +4331,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>148</v>
       </c>
@@ -4354,7 +4354,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>149</v>
       </c>
@@ -4377,7 +4377,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>150</v>
       </c>
@@ -4400,7 +4400,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>151</v>
       </c>
@@ -4423,7 +4423,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>152</v>
       </c>
@@ -4446,7 +4446,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>153</v>
       </c>
@@ -4469,7 +4469,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>154</v>
       </c>
@@ -4492,7 +4492,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>155</v>
       </c>
@@ -4515,7 +4515,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>156</v>
       </c>
@@ -4538,7 +4538,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>157</v>
       </c>
@@ -4561,7 +4561,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>158</v>
       </c>
@@ -4584,7 +4584,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>159</v>
       </c>
@@ -4607,7 +4607,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>160</v>
       </c>
@@ -4630,7 +4630,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>161</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>162</v>
       </c>
@@ -4676,7 +4676,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>163</v>
       </c>
@@ -4696,7 +4696,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>164</v>
       </c>
@@ -4719,7 +4719,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>165</v>
       </c>
@@ -4742,7 +4742,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>166</v>
       </c>
@@ -4765,7 +4765,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>167</v>
       </c>
@@ -4788,7 +4788,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>168</v>
       </c>
@@ -4811,7 +4811,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>169</v>
       </c>
@@ -4834,7 +4834,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>170</v>
       </c>
@@ -4857,7 +4857,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>171</v>
       </c>
@@ -4880,7 +4880,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>172</v>
       </c>
@@ -4903,7 +4903,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>173</v>
       </c>
@@ -4926,7 +4926,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>174</v>
       </c>
@@ -4949,7 +4949,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>175</v>
       </c>
@@ -4972,7 +4972,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>176</v>
       </c>
@@ -4995,7 +4995,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>177</v>
       </c>
@@ -5018,7 +5018,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>178</v>
       </c>
@@ -5041,7 +5041,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>179</v>
       </c>
@@ -5064,7 +5064,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>180</v>
       </c>
@@ -5087,7 +5087,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>181</v>
       </c>
@@ -5110,7 +5110,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>182</v>
       </c>
@@ -5133,7 +5133,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>183</v>
       </c>
@@ -5156,7 +5156,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>184</v>
       </c>
@@ -5176,7 +5176,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>185</v>
       </c>
@@ -5199,7 +5199,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>186</v>
       </c>
@@ -5222,7 +5222,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>187</v>
       </c>
@@ -5245,7 +5245,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>188</v>
       </c>
@@ -5268,7 +5268,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>189</v>
       </c>
@@ -5291,7 +5291,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>190</v>
       </c>
@@ -5314,7 +5314,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>191</v>
       </c>
@@ -5334,7 +5334,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>192</v>
       </c>
@@ -5357,7 +5357,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>193</v>
       </c>
@@ -5380,7 +5380,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>194</v>
       </c>
@@ -5403,7 +5403,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>195</v>
       </c>
@@ -5426,7 +5426,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>196</v>
       </c>
@@ -5449,7 +5449,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>197</v>
       </c>
@@ -5472,7 +5472,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>198</v>
       </c>
@@ -5495,7 +5495,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>199</v>
       </c>
@@ -5515,7 +5515,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>200</v>
       </c>
@@ -5538,7 +5538,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>201</v>
       </c>
@@ -5561,7 +5561,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>202</v>
       </c>
@@ -5584,7 +5584,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>203</v>
       </c>
@@ -5607,7 +5607,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>204</v>
       </c>
@@ -5630,7 +5630,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>205</v>
       </c>
@@ -5653,7 +5653,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>206</v>
       </c>
@@ -5676,7 +5676,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>207</v>
       </c>
@@ -5699,7 +5699,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>208</v>
       </c>
@@ -5719,7 +5719,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>209</v>
       </c>
@@ -5742,7 +5742,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>210</v>
       </c>
@@ -5765,7 +5765,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>211</v>
       </c>
@@ -5788,7 +5788,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>212</v>
       </c>
@@ -5811,7 +5811,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>213</v>
       </c>
@@ -5834,7 +5834,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>214</v>
       </c>
@@ -5857,7 +5857,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>215</v>
       </c>
@@ -5880,7 +5880,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>216</v>
       </c>
@@ -5903,7 +5903,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>217</v>
       </c>
@@ -5926,7 +5926,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>218</v>
       </c>
@@ -5949,7 +5949,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>219</v>
       </c>
@@ -5972,7 +5972,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>220</v>
       </c>
@@ -5995,7 +5995,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>221</v>
       </c>
@@ -6018,7 +6018,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>222</v>
       </c>
@@ -6041,7 +6041,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>223</v>
       </c>
@@ -6064,7 +6064,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>224</v>
       </c>
@@ -6087,7 +6087,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>225</v>
       </c>
@@ -6110,7 +6110,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>226</v>
       </c>
@@ -6133,7 +6133,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>227</v>
       </c>
@@ -6156,7 +6156,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
         <v>228</v>
       </c>
@@ -6179,7 +6179,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
         <v>229</v>
       </c>
@@ -6202,7 +6202,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
         <v>230</v>
       </c>
@@ -6225,7 +6225,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
         <v>231</v>
       </c>
@@ -6248,7 +6248,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
         <v>232</v>
       </c>
@@ -6271,7 +6271,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
         <v>233</v>
       </c>
@@ -6294,7 +6294,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
         <v>234</v>
       </c>
@@ -6317,7 +6317,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
         <v>235</v>
       </c>
@@ -6340,7 +6340,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
         <v>236</v>
       </c>
@@ -6374,25 +6374,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E979612-8BD7-40EA-9D5A-2165C0273E84}">
   <dimension ref="A1:H184"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="23.703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.41015625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.234375" customWidth="1"/>
-    <col min="4" max="4" width="12.41015625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.17578125" customWidth="1"/>
-    <col min="6" max="6" width="11.9375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.19921875" customWidth="1"/>
+    <col min="4" max="4" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.19921875" customWidth="1"/>
+    <col min="6" max="6" width="11.9296875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="13.9375" customWidth="1"/>
+    <col min="8" max="8" width="13.9296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" t="e" cm="1" vm="1">
         <f t="array" ref="A1">_xlfn._xlws.PY(1,1,sales[#All])</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" t="str" cm="1">
         <f t="array" ref="A3:G8">_xlfn._xlws.PY(2,0)</f>
         <v>order_id</v>
@@ -6416,7 +6416,7 @@
         <v>country</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" t="str">
         <v>ORD-0001</v>
       </c>
@@ -6439,7 +6439,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" t="str">
         <v>ORD-0002</v>
       </c>
@@ -6462,7 +6462,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="str">
         <v>ORD-0003</v>
       </c>
@@ -6485,7 +6485,7 @@
         <v>Germany</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" t="str">
         <v>ORD-0004</v>
       </c>
@@ -6508,7 +6508,7 @@
         <v>Germany</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" t="str">
         <v>ORD-0005</v>
       </c>
@@ -6531,7 +6531,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" t="str" cm="1">
         <f t="array" ref="A10:H15">_xlfn._xlws.PY(3,0)</f>
         <v/>
@@ -6558,7 +6558,7 @@
         <v>country</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>195</v>
       </c>
@@ -6584,7 +6584,7 @@
         <v>United Kingdom</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>196</v>
       </c>
@@ -6610,7 +6610,7 @@
         <v>United Kingdom</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>197</v>
       </c>
@@ -6636,7 +6636,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>198</v>
       </c>
@@ -6662,7 +6662,7 @@
         <v>United Kingdom</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>199</v>
       </c>
@@ -6688,7 +6688,7 @@
         <v>Canada</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" t="str" cm="1">
         <f t="array" ref="A17:H22">_xlfn._xlws.PY(4,0)</f>
         <v/>
@@ -6715,116 +6715,116 @@
         <v>country</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18">
-        <v>163</v>
+        <v>110</v>
       </c>
       <c r="B18" t="str">
-        <v>ORD-0164</v>
+        <v>ORD-0111</v>
       </c>
       <c r="C18" t="str">
-        <v>Printer Paper</v>
+        <v>Keyboard</v>
       </c>
       <c r="D18" t="str">
-        <v>Office Supplies</v>
+        <v>Electronics</v>
       </c>
       <c r="E18">
-        <v>6.67</v>
+        <v>475.83</v>
       </c>
       <c r="F18">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G18">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H18" t="str">
         <v>United States</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19">
-        <v>98</v>
+        <v>162</v>
       </c>
       <c r="B19" t="str">
-        <v>ORD-0099</v>
+        <v>ORD-0163</v>
       </c>
       <c r="C19" t="str">
-        <v>Monitor</v>
+        <v>Binder</v>
       </c>
       <c r="D19" t="str">
-        <v>Electronics</v>
+        <v>Office Supplies</v>
       </c>
       <c r="E19">
-        <v>125.76</v>
+        <v>33.159999999999997</v>
       </c>
       <c r="F19">
-        <v>5</v>
-      </c>
-      <c r="G19">
-        <v>43</v>
+        <v>2</v>
+      </c>
+      <c r="G19" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="H19" t="str">
         <v>United States</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A20">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="B20" t="str">
-        <v>ORD-0068</v>
+        <v>ORD-0005</v>
       </c>
       <c r="C20" t="str">
-        <v>Lamp</v>
+        <v>Tablet</v>
       </c>
       <c r="D20" t="str">
-        <v>Furniture</v>
+        <v>Electronics</v>
       </c>
       <c r="E20">
-        <v>301.39</v>
+        <v>479.68</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G20">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="H20" t="str">
         <v>United States</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="B21" t="str">
-        <v>ORD-0110</v>
+        <v>ORD-0103</v>
       </c>
       <c r="C21" t="str">
-        <v>Laptop</v>
+        <v>Bookshelf</v>
       </c>
       <c r="D21" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="E21">
-        <v>215.34</v>
+        <v>369.13</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G21">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="H21" t="str">
-        <v>Germany</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.5">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22">
-        <v>8</v>
+        <v>160</v>
       </c>
       <c r="B22" t="str">
-        <v>ORD-0009</v>
+        <v>ORD-0161</v>
       </c>
       <c r="C22" t="str">
         <v>Binder</v>
@@ -6833,19 +6833,19 @@
         <v>Office Supplies</v>
       </c>
       <c r="E22">
-        <v>9.81</v>
+        <v>30.06</v>
       </c>
       <c r="F22">
         <v>6</v>
       </c>
       <c r="G22">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="H22" t="str">
         <v>Germany</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A24" t="str" cm="1">
         <f t="array" ref="A24:B30">_xlfn._xlws.PY(5,0)</f>
         <v>order_id</v>
@@ -6854,7 +6854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A25" t="str">
         <v>product</v>
       </c>
@@ -6862,7 +6862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A26" t="str">
         <v>category</v>
       </c>
@@ -6870,7 +6870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A27" t="str">
         <v>unit_price</v>
       </c>
@@ -6878,7 +6878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" t="str">
         <v>quantity</v>
       </c>
@@ -6886,15 +6886,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" t="str">
         <v>customer_age</v>
       </c>
       <c r="B29">
-        <v>2.9999999999999997E-4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" t="str">
         <v>country</v>
       </c>
@@ -6902,7 +6902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A32" t="str" cm="1">
         <f t="array" ref="A32:B38">_xlfn._xlws.PY(6,0)</f>
         <v>customer_age</v>
@@ -6911,7 +6911,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" t="str">
         <v>order_id</v>
       </c>
@@ -6919,7 +6919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" t="str">
         <v>product</v>
       </c>
@@ -6927,7 +6927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" t="str">
         <v>category</v>
       </c>
@@ -6935,7 +6935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" t="str">
         <v>unit_price</v>
       </c>
@@ -6943,7 +6943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" t="str">
         <v>quantity</v>
       </c>
@@ -6951,7 +6951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" t="str">
         <v>country</v>
       </c>
@@ -6959,18 +6959,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" cm="1">
         <f t="array" ref="A40:A41">_xlfn._xlws.PY(7,0)</f>
         <v>200</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" t="str" cm="1">
         <f t="array" ref="A43:D51">_xlfn._xlws.PY(8,0)</f>
         <v/>
@@ -6985,7 +6985,7 @@
         <v>customer_age</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" t="str">
         <v>count</v>
       </c>
@@ -6999,7 +6999,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" t="str">
         <v>mean</v>
       </c>
@@ -7013,7 +7013,7 @@
         <v>43.597938144329895</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" t="str">
         <v>std</v>
       </c>
@@ -7027,7 +7027,7 @@
         <v>13.286527356620564</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" t="str">
         <v>min</v>
       </c>
@@ -7041,7 +7041,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48" t="str">
         <v>25%</v>
       </c>
@@ -7055,7 +7055,7 @@
         <v>33.25</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" t="str">
         <v>50%</v>
       </c>
@@ -7069,7 +7069,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" t="str">
         <v>75%</v>
       </c>
@@ -7083,7 +7083,7 @@
         <v>55.75</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" t="str">
         <v>max</v>
       </c>
@@ -7097,7 +7097,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" t="str" cm="1">
         <f t="array" ref="A53:D61">_xlfn._xlws.PY(9,0)</f>
         <v/>
@@ -7112,7 +7112,7 @@
         <v>customer_age</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" t="str">
         <v>count</v>
       </c>
@@ -7126,7 +7126,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" t="str">
         <v>mean</v>
       </c>
@@ -7140,7 +7140,7 @@
         <v>43.597938144329895</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" t="str">
         <v>std</v>
       </c>
@@ -7154,7 +7154,7 @@
         <v>13.286527356620564</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" t="str">
         <v>min</v>
       </c>
@@ -7168,7 +7168,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" t="str">
         <v>10%</v>
       </c>
@@ -7182,7 +7182,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A59" t="str">
         <v>50%</v>
       </c>
@@ -7196,7 +7196,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" t="str">
         <v>90%</v>
       </c>
@@ -7210,7 +7210,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" t="str">
         <v>max</v>
       </c>
@@ -7224,7 +7224,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" t="str" cm="1">
         <f t="array" ref="A63:E67">_xlfn._xlws.PY(10,0)</f>
         <v/>
@@ -7242,7 +7242,7 @@
         <v>country</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A64" t="str">
         <v>count</v>
       </c>
@@ -7259,7 +7259,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A65" t="str">
         <v>unique</v>
       </c>
@@ -7276,7 +7276,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A66" t="str">
         <v>top</v>
       </c>
@@ -7293,7 +7293,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A67" t="str">
         <v>freq</v>
       </c>
@@ -7310,7 +7310,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A69" t="str" cm="1">
         <f t="array" ref="A69:C74">_xlfn._xlws.PY(11,0)</f>
         <v>product</v>
@@ -7322,7 +7322,7 @@
         <v>unit_price</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A70" t="str">
         <v>Desk</v>
       </c>
@@ -7333,7 +7333,7 @@
         <v>68.760000000000005</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A71" t="str">
         <v>Lamp</v>
       </c>
@@ -7344,7 +7344,7 @@
         <v>115.2</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A72" t="str">
         <v>Lamp</v>
       </c>
@@ -7355,7 +7355,7 @@
         <v>69.900000000000006</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A73" t="str">
         <v>Notebook</v>
       </c>
@@ -7366,7 +7366,7 @@
         <v>15.35</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A74" t="str">
         <v>Tablet</v>
       </c>
@@ -7377,38 +7377,38 @@
         <v>479.68</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A76" t="str" cm="1">
         <f t="array" ref="A76:A81">_xlfn._xlws.PY(12,0)</f>
         <v>country</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A77" t="str">
         <v>United States</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A78" t="str">
         <v>United States</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A79" t="str">
         <v>Germany</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A80" t="str">
         <v>Germany</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A81" t="str">
         <v>United States</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A84" t="str" cm="1">
         <f t="array" ref="A84:H89">_xlfn._xlws.PY(13,0)</f>
         <v/>
@@ -7435,7 +7435,7 @@
         <v>country</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>0</v>
       </c>
@@ -7461,7 +7461,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>1</v>
       </c>
@@ -7487,7 +7487,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>4</v>
       </c>
@@ -7513,7 +7513,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>11</v>
       </c>
@@ -7539,7 +7539,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>13</v>
       </c>
@@ -7565,7 +7565,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A91" t="str" cm="1">
         <f t="array" ref="A91:H96">_xlfn._xlws.PY(14,0)</f>
         <v/>
@@ -7592,7 +7592,7 @@
         <v>country</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>0</v>
       </c>
@@ -7618,7 +7618,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>1</v>
       </c>
@@ -7644,7 +7644,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>4</v>
       </c>
@@ -7670,7 +7670,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>11</v>
       </c>
@@ -7696,7 +7696,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>13</v>
       </c>
@@ -7722,7 +7722,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A98" t="str" cm="1">
         <f t="array" ref="A98:H103">_xlfn._xlws.PY(15,0)</f>
         <v/>
@@ -7749,7 +7749,7 @@
         <v>country</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>0</v>
       </c>
@@ -7775,7 +7775,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>1</v>
       </c>
@@ -7801,7 +7801,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>4</v>
       </c>
@@ -7827,7 +7827,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A102">
         <v>11</v>
       </c>
@@ -7853,7 +7853,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A103">
         <v>13</v>
       </c>
@@ -7879,7 +7879,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A105" t="str" cm="1">
         <f t="array" ref="A105:H110">_xlfn._xlws.PY(16,0)</f>
         <v/>
@@ -7906,7 +7906,7 @@
         <v>country</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A106">
         <v>48</v>
       </c>
@@ -7932,7 +7932,7 @@
         <v>Australia</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A107">
         <v>79</v>
       </c>
@@ -7958,7 +7958,7 @@
         <v>Canada</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A108">
         <v>99</v>
       </c>
@@ -7984,7 +7984,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A109">
         <v>142</v>
       </c>
@@ -8010,7 +8010,7 @@
         <v>Germany</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A110">
         <v>21</v>
       </c>
@@ -8036,7 +8036,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A113" t="str" cm="1">
         <f t="array" ref="A113:H118">_xlfn._xlws.PY(17,0)</f>
         <v/>
@@ -8063,7 +8063,7 @@
         <v>country</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A114">
         <v>113</v>
       </c>
@@ -8089,7 +8089,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A115">
         <v>165</v>
       </c>
@@ -8115,7 +8115,7 @@
         <v>Germany</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A116">
         <v>45</v>
       </c>
@@ -8141,7 +8141,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A117">
         <v>40</v>
       </c>
@@ -8167,7 +8167,7 @@
         <v>Germany</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A118">
         <v>152</v>
       </c>
@@ -8193,7 +8193,7 @@
         <v>Canada</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A121" t="str" cm="1">
         <f t="array" ref="A121:H126">_xlfn._xlws.PY(18,0)</f>
         <v/>
@@ -8220,7 +8220,7 @@
         <v>country</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A122">
         <v>48</v>
       </c>
@@ -8246,7 +8246,7 @@
         <v>Australia</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A123">
         <v>32</v>
       </c>
@@ -8272,7 +8272,7 @@
         <v>Australia</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A124">
         <v>119</v>
       </c>
@@ -8298,7 +8298,7 @@
         <v>Australia</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A125">
         <v>181</v>
       </c>
@@ -8324,7 +8324,7 @@
         <v>Australia</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A126">
         <v>34</v>
       </c>
@@ -8350,7 +8350,7 @@
         <v>Australia</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A129" t="str" cm="1">
         <f t="array" ref="A129:H134">_xlfn._xlws.PY(19,0)</f>
         <v/>
@@ -8377,7 +8377,7 @@
         <v>country</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A130">
         <v>113</v>
       </c>
@@ -8403,7 +8403,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A131">
         <v>165</v>
       </c>
@@ -8429,7 +8429,7 @@
         <v>Germany</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A132">
         <v>45</v>
       </c>
@@ -8455,7 +8455,7 @@
         <v>United States</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A133">
         <v>40</v>
       </c>
@@ -8481,7 +8481,7 @@
         <v>Germany</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A134">
         <v>152</v>
       </c>
@@ -8507,7 +8507,7 @@
         <v>Canada</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A136" t="str" cm="1">
         <f t="array" ref="A136:B141">_xlfn._xlws.PY(20,0)</f>
         <v>country</v>
@@ -8516,7 +8516,7 @@
         <v>count</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A137" t="str">
         <v>United States</v>
       </c>
@@ -8524,7 +8524,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A138" t="str">
         <v>Germany</v>
       </c>
@@ -8532,7 +8532,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A139" t="str">
         <v>United Kingdom</v>
       </c>
@@ -8540,7 +8540,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A140" t="str">
         <v>Canada</v>
       </c>
@@ -8548,7 +8548,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A141" t="str">
         <v>Australia</v>
       </c>
@@ -8556,7 +8556,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A144" t="str" cm="1">
         <f t="array" ref="A144:B147">_xlfn._xlws.PY(21,0)</f>
         <v>category</v>
@@ -8565,7 +8565,7 @@
         <v>proportion</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A145" t="str">
         <v>Office Supplies</v>
       </c>
@@ -8573,7 +8573,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A146" t="str">
         <v>Electronics</v>
       </c>
@@ -8581,7 +8581,7 @@
         <v>0.32500000000000001</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A147" t="str">
         <v>Furniture</v>
       </c>
@@ -8589,7 +8589,7 @@
         <v>0.27500000000000002</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A149" t="str" cm="1">
         <f t="array" ref="A149:B154">_xlfn._xlws.PY(22,0)</f>
         <v>country</v>
@@ -8598,7 +8598,7 @@
         <v>unit_price</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A150" t="str">
         <v>Australia</v>
       </c>
@@ -8606,7 +8606,7 @@
         <v>167.16199999999998</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A151" t="str">
         <v>Canada</v>
       </c>
@@ -8614,7 +8614,7 @@
         <v>201.18230769230769</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A152" t="str">
         <v>Germany</v>
       </c>
@@ -8622,7 +8622,7 @@
         <v>182.58790697674419</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A153" t="str">
         <v>United Kingdom</v>
       </c>
@@ -8630,7 +8630,7 @@
         <v>274.43128205128204</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A154" t="str">
         <v>United States</v>
       </c>
@@ -8638,7 +8638,7 @@
         <v>209.05701298701297</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A156" t="str" cm="1">
         <f t="array" ref="A156:B159">_xlfn._xlws.PY(23,0)</f>
         <v>category</v>
@@ -8647,7 +8647,7 @@
         <v>quantity</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A157" t="str">
         <v>Electronics</v>
       </c>
@@ -8655,7 +8655,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A158" t="str">
         <v>Furniture</v>
       </c>
@@ -8663,7 +8663,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.5">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A159" t="str">
         <v>Office Supplies</v>
       </c>
@@ -8671,7 +8671,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A161" t="str" cm="1">
         <f t="array" ref="A161:C176">_xlfn._xlws.PY(24,0)</f>
         <v>country</v>
@@ -8683,7 +8683,7 @@
         <v>unit_price</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A162" t="str">
         <v>Australia</v>
       </c>
@@ -8694,7 +8694,7 @@
         <v>270.6516666666667</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A163" t="str">
         <v>Australia</v>
       </c>
@@ -8705,7 +8705,7 @@
         <v>256.68</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A164" t="str">
         <v>Australia</v>
       </c>
@@ -8716,7 +8716,7 @@
         <v>18.91333333333333</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A165" t="str">
         <v>Canada</v>
       </c>
@@ -8727,7 +8727,7 @@
         <v>274.04250000000002</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A166" t="str">
         <v>Canada</v>
       </c>
@@ -8738,7 +8738,7 @@
         <v>529.45000000000005</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A167" t="str">
         <v>Canada</v>
       </c>
@@ -8749,7 +8749,7 @@
         <v>30.088461538461541</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A168" t="str">
         <v>Germany</v>
       </c>
@@ -8760,7 +8760,7 @@
         <v>230.67818181818183</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A169" t="str">
         <v>Germany</v>
       </c>
@@ -8771,7 +8771,7 @@
         <v>350.0864285714286</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A170" t="str">
         <v>Germany</v>
       </c>
@@ -8782,7 +8782,7 @@
         <v>22.922777777777778</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A171" t="str">
         <v>United Kingdom</v>
       </c>
@@ -8793,7 +8793,7 @@
         <v>272.95764705882351</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A172" t="str">
         <v>United Kingdom</v>
       </c>
@@ -8804,7 +8804,7 @@
         <v>529.8054545454545</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A173" t="str">
         <v>United Kingdom</v>
       </c>
@@ -8815,7 +8815,7 @@
         <v>21.334545454545456</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A174" t="str">
         <v>United States</v>
       </c>
@@ -8826,7 +8826,7 @@
         <v>296.6995652173913</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A175" t="str">
         <v>United States</v>
       </c>
@@ -8837,7 +8837,7 @@
         <v>383.92954545454546</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.5">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A176" t="str">
         <v>United States</v>
       </c>
@@ -8848,7 +8848,7 @@
         <v>25.839062500000001</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A178" t="str" cm="1">
         <f t="array" ref="A178:D184">_xlfn._xlws.PY(25,0)</f>
         <v/>
@@ -8863,7 +8863,7 @@
         <v>max</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A179" t="str">
         <v>country</v>
       </c>
@@ -8877,7 +8877,7 @@
         <v/>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A180" t="str">
         <v>Australia</v>
       </c>
@@ -8891,7 +8891,7 @@
         <v>486.65</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A181" t="str">
         <v>Canada</v>
       </c>
@@ -8905,7 +8905,7 @@
         <v>732.96</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A182" t="str">
         <v>Germany</v>
       </c>
@@ -8919,7 +8919,7 @@
         <v>754.29</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A183" t="str">
         <v>United Kingdom</v>
       </c>
@@ -8933,7 +8933,7 @@
         <v>689.59</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.5">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A184" t="str">
         <v>United States</v>
       </c>

--- a/ch_02/ch_02_solution.xlsx
+++ b/ch_02/ch_02_solution.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30515"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30610"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BAB798-30DC-45AB-BE45-757F4853DD5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5150410-B72E-4E57-98AD-204ECFE28472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="nyc" sheetId="1" r:id="rId1"/>
@@ -6717,132 +6717,132 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="B18" t="str">
-        <v>ORD-0111</v>
+        <v>ORD-0041</v>
       </c>
       <c r="C18" t="str">
-        <v>Keyboard</v>
+        <v>Bookshelf</v>
       </c>
       <c r="D18" t="str">
-        <v>Electronics</v>
+        <v>Furniture</v>
       </c>
       <c r="E18">
-        <v>475.83</v>
+        <v>751.03</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G18">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="H18" t="str">
-        <v>United States</v>
+        <v>Germany</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="B19" t="str">
-        <v>ORD-0163</v>
+        <v>ORD-0177</v>
       </c>
       <c r="C19" t="str">
-        <v>Binder</v>
+        <v>Printer Paper</v>
       </c>
       <c r="D19" t="str">
         <v>Office Supplies</v>
       </c>
       <c r="E19">
-        <v>33.159999999999997</v>
+        <v>25.53</v>
       </c>
       <c r="F19">
-        <v>2</v>
-      </c>
-      <c r="G19" t="e">
-        <v>#NUM!</v>
+        <v>8</v>
+      </c>
+      <c r="G19">
+        <v>26</v>
       </c>
       <c r="H19" t="str">
-        <v>United States</v>
+        <v>Canada</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A20">
+        <v>55</v>
+      </c>
+      <c r="B20" t="str">
+        <v>ORD-0056</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Printer Paper</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="E20">
+        <v>43.21</v>
+      </c>
+      <c r="F20">
         <v>4</v>
       </c>
-      <c r="B20" t="str">
-        <v>ORD-0005</v>
-      </c>
-      <c r="C20" t="str">
-        <v>Tablet</v>
-      </c>
-      <c r="D20" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="E20">
-        <v>479.68</v>
-      </c>
-      <c r="F20">
-        <v>6</v>
-      </c>
       <c r="G20">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H20" t="str">
-        <v>United States</v>
+        <v>Canada</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21">
-        <v>102</v>
+        <v>157</v>
       </c>
       <c r="B21" t="str">
-        <v>ORD-0103</v>
+        <v>ORD-0158</v>
       </c>
       <c r="C21" t="str">
-        <v>Bookshelf</v>
+        <v>Headphones</v>
       </c>
       <c r="D21" t="str">
-        <v>Furniture</v>
+        <v>Electronics</v>
       </c>
       <c r="E21">
-        <v>369.13</v>
+        <v>459.17</v>
       </c>
       <c r="F21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G21">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H21" t="str">
-        <v>United States</v>
+        <v>Germany</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="B22" t="str">
-        <v>ORD-0161</v>
+        <v>ORD-0170</v>
       </c>
       <c r="C22" t="str">
-        <v>Binder</v>
+        <v>Keyboard</v>
       </c>
       <c r="D22" t="str">
-        <v>Office Supplies</v>
+        <v>Electronics</v>
       </c>
       <c r="E22">
-        <v>30.06</v>
+        <v>122.47</v>
       </c>
       <c r="F22">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G22">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H22" t="str">
-        <v>Germany</v>
+        <v>United Kingdom</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.45">
@@ -6913,7 +6913,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" t="str">
-        <v>order_id</v>
+        <v>product</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -6921,7 +6921,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" t="str">
-        <v>product</v>
+        <v>order_id</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -7281,7 +7281,7 @@
         <v>top</v>
       </c>
       <c r="B66" t="str">
-        <v>ORD-0001</v>
+        <v>ORD-0185</v>
       </c>
       <c r="C66" t="str">
         <v>Notebook</v>
